--- a/reports/Debug-snowbowl-20251216/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/Month to Date (Actual)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
     <t>Snowbowl Uplift Tickets</t>
@@ -431,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C2" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,7 +448,7 @@
         <v>45994</v>
       </c>
       <c r="C3" s="2">
-        <v>593</v>
+        <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45996</v>
+        <v>45994</v>
       </c>
       <c r="C4" s="2">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +473,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +487,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="C6" s="2">
-        <v>1091</v>
+        <v>173</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,10 +504,10 @@
         <v>45999</v>
       </c>
       <c r="C7" s="2">
-        <v>1058</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>46000</v>
       </c>
       <c r="C8" s="2">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>913</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>46002</v>
       </c>
       <c r="C10" s="2">
-        <v>1080</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>46003</v>
       </c>
       <c r="C11" s="2">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>46005</v>
+        <v>46003</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>1104</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>46005</v>
+        <v>46004</v>
       </c>
       <c r="C13" s="2">
-        <v>1548</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>46006</v>
+        <v>46005</v>
       </c>
       <c r="C15" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="C16" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -641,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>1389</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,10 +669,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45994</v>
+        <v>46007</v>
       </c>
       <c r="C19" s="2">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -683,10 +683,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45995</v>
+        <v>45993</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -697,10 +697,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45996</v>
+        <v>45994</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="C22" s="2">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="C23" s="2">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45999</v>
+        <v>45996</v>
       </c>
       <c r="C24" s="2">
-        <v>9</v>
+        <v>1091</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C25" s="2">
-        <v>79</v>
+        <v>1058</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +767,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C26" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,7 +784,7 @@
         <v>46002</v>
       </c>
       <c r="C27" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,10 +798,10 @@
         <v>46002</v>
       </c>
       <c r="C28" s="2">
-        <v>741</v>
+        <v>1080</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>46003</v>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="C30" s="2">
-        <v>417</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>46005</v>
       </c>
       <c r="C31" s="2">
-        <v>12</v>
+        <v>1548</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C32" s="2">
-        <v>993</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C33" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>46007</v>
+        <v>45992</v>
       </c>
       <c r="C34" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +896,10 @@
         <v>45992</v>
       </c>
       <c r="C35" s="2">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,10 +907,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="C36" s="2">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -921,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="C37" s="2">
-        <v>488</v>
+        <v>54</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -935,10 +935,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -949,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="C39" s="2">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,10 +963,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45995</v>
+        <v>45997</v>
       </c>
       <c r="C40" s="2">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -977,10 +977,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45995</v>
+        <v>45998</v>
       </c>
       <c r="C41" s="2">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -991,10 +991,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="C42" s="2">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1005,10 +1005,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C43" s="2">
-        <v>1326</v>
+        <v>79</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1019,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="C44" s="2">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="C45" s="2">
-        <v>1627</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45998</v>
+        <v>46002</v>
       </c>
       <c r="C46" s="2">
-        <v>21</v>
+        <v>741</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1061,10 +1061,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45998</v>
+        <v>46003</v>
       </c>
       <c r="C47" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1075,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="C48" s="2">
-        <v>718</v>
+        <v>417</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,10 +1089,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1103,10 +1103,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>46000</v>
+        <v>46005</v>
       </c>
       <c r="C50" s="2">
-        <v>7</v>
+        <v>993</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1117,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C51" s="2">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="C52" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,7 +1148,7 @@
         <v>45992</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,7 +1162,7 @@
         <v>45993</v>
       </c>
       <c r="C54" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,7 +1176,7 @@
         <v>45993</v>
       </c>
       <c r="C55" s="2">
-        <v>67</v>
+        <v>738</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>7</v>
@@ -1187,10 +1187,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45994</v>
+        <v>45993</v>
       </c>
       <c r="C56" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -1201,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45995</v>
+        <v>45994</v>
       </c>
       <c r="C57" s="2">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1215,13 +1215,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="C58" s="2">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1229,13 +1229,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,10 +1243,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45998</v>
+        <v>45997</v>
       </c>
       <c r="C60" s="2">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1257,10 +1257,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45998</v>
+        <v>45997</v>
       </c>
       <c r="C61" s="2">
-        <v>1151</v>
+        <v>1192</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1274,7 +1274,7 @@
         <v>45999</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1285,13 +1285,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="C63" s="2">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>46000</v>
       </c>
       <c r="C64" s="2">
-        <v>53</v>
+        <v>570</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>46001</v>
       </c>
       <c r="C65" s="2">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1327,10 +1327,10 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C66" s="2">
-        <v>725</v>
+        <v>997</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1341,13 +1341,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="C67" s="2">
-        <v>13</v>
+        <v>245</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1355,13 +1355,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="C68" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1369,10 +1369,10 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>46004</v>
+        <v>45992</v>
       </c>
       <c r="C69" s="2">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1383,10 +1383,10 @@
         <v>4</v>
       </c>
       <c r="B70" s="2">
-        <v>46004</v>
+        <v>45992</v>
       </c>
       <c r="C70" s="2">
-        <v>847</v>
+        <v>656</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1397,13 +1397,13 @@
         <v>4</v>
       </c>
       <c r="B71" s="2">
-        <v>46005</v>
+        <v>45992</v>
       </c>
       <c r="C71" s="2">
-        <v>1</v>
+        <v>797</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>4</v>
       </c>
       <c r="B72" s="2">
-        <v>46006</v>
+        <v>45995</v>
       </c>
       <c r="C72" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1425,10 +1425,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="2">
-        <v>46007</v>
+        <v>45995</v>
       </c>
       <c r="C73" s="2">
-        <v>574</v>
+        <v>803</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1439,13 +1439,13 @@
         <v>4</v>
       </c>
       <c r="B74" s="2">
-        <v>45992</v>
+        <v>45995</v>
       </c>
       <c r="C74" s="2">
-        <v>61</v>
+        <v>865</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B75" s="2">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="C75" s="2">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1467,13 +1467,13 @@
         <v>4</v>
       </c>
       <c r="B76" s="2">
-        <v>45993</v>
+        <v>45997</v>
       </c>
       <c r="C76" s="2">
-        <v>738</v>
+        <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1481,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="B77" s="2">
-        <v>45993</v>
+        <v>45998</v>
       </c>
       <c r="C77" s="2">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1495,13 +1495,13 @@
         <v>4</v>
       </c>
       <c r="B78" s="2">
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="C78" s="2">
-        <v>10</v>
+        <v>1401</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,13 +1509,13 @@
         <v>4</v>
       </c>
       <c r="B79" s="2">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="C79" s="2">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1523,13 +1523,13 @@
         <v>4</v>
       </c>
       <c r="B80" s="2">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="C80" s="2">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1537,10 +1537,10 @@
         <v>4</v>
       </c>
       <c r="B81" s="2">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="C81" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1551,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B82" s="2">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="C82" s="2">
-        <v>1192</v>
+        <v>1004</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B83" s="2">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="C83" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="B84" s="2">
-        <v>45999</v>
+        <v>46002</v>
       </c>
       <c r="C84" s="2">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1593,13 +1593,13 @@
         <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C85" s="2">
-        <v>570</v>
+        <v>91</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C86" s="2">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="C87" s="2">
-        <v>997</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1635,13 +1635,13 @@
         <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="C88" s="2">
-        <v>245</v>
+        <v>2</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1649,13 +1649,13 @@
         <v>4</v>
       </c>
       <c r="B89" s="2">
-        <v>46007</v>
+        <v>46005</v>
       </c>
       <c r="C89" s="2">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1663,10 +1663,10 @@
         <v>4</v>
       </c>
       <c r="B90" s="2">
-        <v>45992</v>
+        <v>46005</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1677,13 +1677,13 @@
         <v>4</v>
       </c>
       <c r="B91" s="2">
-        <v>45994</v>
+        <v>46005</v>
       </c>
       <c r="C91" s="2">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1691,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="B92" s="2">
-        <v>45994</v>
+        <v>46007</v>
       </c>
       <c r="C92" s="2">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,10 +1705,10 @@
         <v>4</v>
       </c>
       <c r="B93" s="2">
-        <v>45997</v>
+        <v>46007</v>
       </c>
       <c r="C93" s="2">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1719,13 +1719,13 @@
         <v>4</v>
       </c>
       <c r="B94" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C94" s="2">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1733,10 +1733,10 @@
         <v>4</v>
       </c>
       <c r="B95" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C95" s="2">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1747,13 +1747,13 @@
         <v>4</v>
       </c>
       <c r="B96" s="2">
-        <v>46000</v>
+        <v>45995</v>
       </c>
       <c r="C96" s="2">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1761,13 @@
         <v>4</v>
       </c>
       <c r="B97" s="2">
-        <v>46000</v>
+        <v>45998</v>
       </c>
       <c r="C97" s="2">
-        <v>913</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,13 +1775,13 @@
         <v>4</v>
       </c>
       <c r="B98" s="2">
-        <v>46002</v>
+        <v>45998</v>
       </c>
       <c r="C98" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1789,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1803,13 +1803,13 @@
         <v>4</v>
       </c>
       <c r="B100" s="2">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C100" s="2">
-        <v>1104</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1817,13 +1817,13 @@
         <v>4</v>
       </c>
       <c r="B101" s="2">
-        <v>46004</v>
+        <v>46001</v>
       </c>
       <c r="C101" s="2">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1831,13 @@
         <v>4</v>
       </c>
       <c r="B102" s="2">
-        <v>46004</v>
+        <v>46002</v>
       </c>
       <c r="C102" s="2">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,10 +1845,10 @@
         <v>4</v>
       </c>
       <c r="B103" s="2">
-        <v>46005</v>
+        <v>46003</v>
       </c>
       <c r="C103" s="2">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1859,10 +1859,10 @@
         <v>4</v>
       </c>
       <c r="B104" s="2">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="C104" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,13 +1873,13 @@
         <v>4</v>
       </c>
       <c r="B105" s="2">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="C105" s="2">
-        <v>1389</v>
+        <v>1588</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1887,10 +1887,10 @@
         <v>4</v>
       </c>
       <c r="B106" s="2">
-        <v>46006</v>
+        <v>46005</v>
       </c>
       <c r="C106" s="2">
-        <v>91</v>
+        <v>339</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>8</v>
@@ -1901,10 +1901,10 @@
         <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C107" s="2">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1915,13 +1915,13 @@
         <v>4</v>
       </c>
       <c r="B108" s="2">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="C108" s="2">
-        <v>100</v>
+        <v>661</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1929,13 +1929,13 @@
         <v>4</v>
       </c>
       <c r="B109" s="2">
-        <v>45994</v>
+        <v>46007</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>1416</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,13 +1943,13 @@
         <v>4</v>
       </c>
       <c r="B110" s="2">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="C110" s="2">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1957,10 @@
         <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C111" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1971,13 +1971,13 @@
         <v>4</v>
       </c>
       <c r="B112" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C112" s="2">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1985,13 +1985,13 @@
         <v>4</v>
       </c>
       <c r="B113" s="2">
-        <v>46000</v>
+        <v>45994</v>
       </c>
       <c r="C113" s="2">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1999,10 +1999,10 @@
         <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="C114" s="2">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2013,13 +2013,13 @@
         <v>4</v>
       </c>
       <c r="B115" s="2">
-        <v>46001</v>
+        <v>45997</v>
       </c>
       <c r="C115" s="2">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2027,13 +2027,13 @@
         <v>4</v>
       </c>
       <c r="B116" s="2">
-        <v>46002</v>
+        <v>45997</v>
       </c>
       <c r="C116" s="2">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,10 +2041,10 @@
         <v>4</v>
       </c>
       <c r="B117" s="2">
-        <v>46003</v>
+        <v>45998</v>
       </c>
       <c r="C117" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2055,10 +2055,10 @@
         <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>46004</v>
+        <v>45998</v>
       </c>
       <c r="C118" s="2">
-        <v>10</v>
+        <v>1151</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>5</v>
@@ -2069,13 +2069,13 @@
         <v>4</v>
       </c>
       <c r="B119" s="2">
-        <v>46004</v>
+        <v>45999</v>
       </c>
       <c r="C119" s="2">
-        <v>1588</v>
+        <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,13 +2083,13 @@
         <v>4</v>
       </c>
       <c r="B120" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C120" s="2">
-        <v>339</v>
+        <v>7</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2097,13 +2097,13 @@
         <v>4</v>
       </c>
       <c r="B121" s="2">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C121" s="2">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,10 +2111,10 @@
         <v>4</v>
       </c>
       <c r="B122" s="2">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C122" s="2">
-        <v>661</v>
+        <v>97</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2125,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="B123" s="2">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C123" s="2">
-        <v>1416</v>
+        <v>725</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,10 +2139,10 @@
         <v>4</v>
       </c>
       <c r="B124" s="2">
-        <v>45992</v>
+        <v>46003</v>
       </c>
       <c r="C124" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2153,13 +2153,13 @@
         <v>4</v>
       </c>
       <c r="B125" s="2">
-        <v>45992</v>
+        <v>46003</v>
       </c>
       <c r="C125" s="2">
-        <v>656</v>
+        <v>68</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2167,13 +2167,13 @@
         <v>4</v>
       </c>
       <c r="B126" s="2">
-        <v>45992</v>
+        <v>46004</v>
       </c>
       <c r="C126" s="2">
-        <v>797</v>
+        <v>70</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,10 +2181,10 @@
         <v>4</v>
       </c>
       <c r="B127" s="2">
-        <v>45995</v>
+        <v>46004</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>847</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>5</v>
@@ -2195,10 +2195,10 @@
         <v>4</v>
       </c>
       <c r="B128" s="2">
-        <v>45995</v>
+        <v>46005</v>
       </c>
       <c r="C128" s="2">
-        <v>803</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>5</v>
@@ -2209,13 +2209,13 @@
         <v>4</v>
       </c>
       <c r="B129" s="2">
-        <v>45995</v>
+        <v>46006</v>
       </c>
       <c r="C129" s="2">
-        <v>865</v>
+        <v>5</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2223,13 +2223,13 @@
         <v>4</v>
       </c>
       <c r="B130" s="2">
-        <v>45996</v>
+        <v>46007</v>
       </c>
       <c r="C130" s="2">
-        <v>93</v>
+        <v>574</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2237,13 +2237,13 @@
         <v>4</v>
       </c>
       <c r="B131" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,10 +2251,10 @@
         <v>4</v>
       </c>
       <c r="B132" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>5</v>
@@ -2265,13 +2265,13 @@
         <v>4</v>
       </c>
       <c r="B133" s="2">
-        <v>45998</v>
+        <v>45993</v>
       </c>
       <c r="C133" s="2">
-        <v>1401</v>
+        <v>488</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,13 +2279,13 @@
         <v>4</v>
       </c>
       <c r="B134" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C134" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2293,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="B135" s="2">
-        <v>46001</v>
+        <v>45994</v>
       </c>
       <c r="C135" s="2">
-        <v>8</v>
+        <v>711</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2307,10 +2307,10 @@
         <v>4</v>
       </c>
       <c r="B136" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2321,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B137" s="2">
-        <v>46001</v>
+        <v>45995</v>
       </c>
       <c r="C137" s="2">
-        <v>1004</v>
+        <v>64</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2335,10 +2335,10 @@
         <v>4</v>
       </c>
       <c r="B138" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C138" s="2">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,10 +2349,10 @@
         <v>4</v>
       </c>
       <c r="B139" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C139" s="2">
-        <v>1</v>
+        <v>1326</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2363,13 +2363,13 @@
         <v>4</v>
       </c>
       <c r="B140" s="2">
-        <v>46002</v>
+        <v>45997</v>
       </c>
       <c r="C140" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2377,13 +2377,13 @@
         <v>4</v>
       </c>
       <c r="B141" s="2">
-        <v>46003</v>
+        <v>45997</v>
       </c>
       <c r="C141" s="2">
-        <v>1</v>
+        <v>1627</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2391,10 +2391,10 @@
         <v>4</v>
       </c>
       <c r="B142" s="2">
-        <v>46004</v>
+        <v>45998</v>
       </c>
       <c r="C142" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>5</v>
@@ -2405,10 +2405,10 @@
         <v>4</v>
       </c>
       <c r="B143" s="2">
-        <v>46005</v>
+        <v>45998</v>
       </c>
       <c r="C143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2419,10 +2419,10 @@
         <v>4</v>
       </c>
       <c r="B144" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C144" s="2">
-        <v>2</v>
+        <v>718</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,10 +2433,10 @@
         <v>4</v>
       </c>
       <c r="B145" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C145" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>5</v>
@@ -2447,13 +2447,13 @@
         <v>4</v>
       </c>
       <c r="B146" s="2">
-        <v>46005</v>
+        <v>46000</v>
       </c>
       <c r="C146" s="2">
-        <v>187</v>
+        <v>7</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2461,10 +2461,10 @@
         <v>4</v>
       </c>
       <c r="B147" s="2">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C147" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2475,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C148" s="2">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
